--- a/public/downloads/edusad-anketa-obrazec.xlsx
+++ b/public/downloads/edusad-anketa-obrazec.xlsx
@@ -194,10 +194,10 @@
     <t>Адрес по-русски *</t>
   </si>
   <si>
-    <t>г. Актобе, пр. Абилкайыр хана, 41</t>
-  </si>
-  <si>
-    <t>Улица и дом: г. Актобе, пр. Санкибай батыра, 74</t>
+    <t>г. Шымкент, ул. Абая, 41</t>
+  </si>
+  <si>
+    <t>Город, улица и дом — с городом сад точно встанет на карту: г. Шымкент, ул. Абая, 12</t>
   </si>
   <si>
     <t>addressKk</t>
@@ -206,7 +206,7 @@
     <t>Мекенжайы қазақша</t>
   </si>
   <si>
-    <t>Ақтөбе қ., Әбілқайыр хан даңғылы, 41</t>
+    <t>Шымкент қ., Абай к-сі, 41</t>
   </si>
   <si>
     <t>Адрес по-казахски.</t>
